--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\Cursos\0. Proyectos personales\16. Simulacion liga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorios\simulador_liga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB4C16A-083C-478A-934C-A75001647D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59271E2-87E5-40AA-92BD-B2B83D9857A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{981120EA-7AB1-43B7-91BA-6F2090A6BD15}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{981120EA-7AB1-43B7-91BA-6F2090A6BD15}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="26">
   <si>
     <t>Equipo</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Junior</t>
   </si>
   <si>
-    <t>La Equidad</t>
-  </si>
-  <si>
     <t>América de Cali</t>
   </si>
   <si>
@@ -70,9 +67,6 @@
     <t>Atlético Nacional</t>
   </si>
   <si>
-    <t>Fortaleza CEIF</t>
-  </si>
-  <si>
     <t>Águilas Doradas</t>
   </si>
   <si>
@@ -88,18 +82,9 @@
     <t>Boyacá Chicó</t>
   </si>
   <si>
-    <t>Envigado F. C.</t>
-  </si>
-  <si>
-    <t>Alianza F. C.</t>
-  </si>
-  <si>
     <t>Deportivo Pasto</t>
   </si>
   <si>
-    <t>Patriotas</t>
-  </si>
-  <si>
     <t>Posicion actual</t>
   </si>
   <si>
@@ -113,6 +98,21 @@
   </si>
   <si>
     <t>Equipo Visitante</t>
+  </si>
+  <si>
+    <t>Internacional de Bogotá</t>
+  </si>
+  <si>
+    <t>Llaneros</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Cúcuta Deportivo</t>
+  </si>
+  <si>
+    <t>Alianza Valledupar</t>
   </si>
 </sst>
 </file>
@@ -475,16 +475,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -492,13 +492,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -506,13 +506,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -520,13 +520,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -534,13 +534,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -548,13 +548,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -562,13 +562,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -576,13 +576,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -590,13 +590,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -604,13 +604,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -618,13 +618,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -632,13 +632,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12">
-        <v>-11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -646,13 +646,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -660,13 +660,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -674,13 +674,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -688,13 +688,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>16</v>
       </c>
       <c r="D16">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -702,13 +702,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -716,13 +716,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18">
-        <v>-8</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -730,13 +730,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D19">
-        <v>-10</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -744,13 +744,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>-11</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -758,13 +758,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>-10</v>
+        <v>-14</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703ED327-A2DA-41D0-A033-E2DACFA7FACE}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="22.21875" bestFit="1" customWidth="1"/>
@@ -782,42 +782,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -825,103 +825,103 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -929,23 +929,183 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorios\simulador_liga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59271E2-87E5-40AA-92BD-B2B83D9857A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014EC754-7FA8-40F0-9365-AFC5B412A13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{981120EA-7AB1-43B7-91BA-6F2090A6BD15}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{981120EA-7AB1-43B7-91BA-6F2090A6BD15}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="26">
   <si>
     <t>Equipo</t>
   </si>
@@ -148,8 +148,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,6 +472,7 @@
     <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -495,10 +497,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -509,10 +511,10 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -526,7 +528,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -537,7 +539,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -590,13 +592,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>22</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -604,13 +606,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -618,13 +620,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -632,13 +634,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -646,13 +648,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>19</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -660,13 +662,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -716,13 +718,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>-13</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -730,13 +732,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>-13</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -761,10 +763,10 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>-14</v>
+        <v>-15</v>
       </c>
     </row>
   </sheetData>
@@ -774,337 +776,321 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703ED327-A2DA-41D0-A033-E2DACFA7FACE}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="22.21875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B38" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>2</v>
-      </c>
-      <c r="B40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="B39" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorios\simulador_liga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014EC754-7FA8-40F0-9365-AFC5B412A13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06814708-BF81-4503-B7A9-188ADBE98B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{981120EA-7AB1-43B7-91BA-6F2090A6BD15}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{981120EA-7AB1-43B7-91BA-6F2090A6BD15}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabla" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>Equipo</t>
   </si>
@@ -148,9 +148,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,7 +471,7 @@
     <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -497,10 +496,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -511,7 +510,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -522,13 +521,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -536,13 +535,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -550,13 +549,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -564,13 +563,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -578,13 +577,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -592,13 +591,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -606,13 +605,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -620,13 +619,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -634,13 +633,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -651,10 +650,10 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -662,13 +661,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -676,10 +675,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -693,7 +692,7 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>-6</v>
@@ -707,10 +706,10 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17">
-        <v>-6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -721,10 +720,10 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18">
-        <v>-12</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -735,10 +734,10 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>-14</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -749,10 +748,10 @@
         <v>14</v>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D20">
-        <v>-10</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -763,10 +762,10 @@
         <v>5</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>-15</v>
+        <v>-16</v>
       </c>
     </row>
   </sheetData>
@@ -776,321 +775,97 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703ED327-A2DA-41D0-A033-E2DACFA7FACE}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="22.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="B11" t="s">
         <v>5</v>
       </c>
     </row>
